--- a/human_validation/judge/kor/judge_D010_S003_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S003_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,124 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요—저는 스미스 선생입니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제 이름을 부르는 소리가 계속 들려서 왔어요. 집에 있을 땐 복도 쪽에서 들리는 것 같고, 창고에서도 한 번 그랬는데—아무도 없었어요. 남편이 바로 옆에 서 있는 것처럼 진짜같이 들려서, 그게 무서웠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이렇게 이름 부르는 소리를 들으신 지 얼마나 되셨나요—며칠, 몇 주, 아니면 그보다 더 오래되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 이렇게 병원까지 오게 될 만큼 무서워진 지는 꽤 됐어요. 집에서는 복도 쪽에서 제 이름이 들리고, 창고에서도 한 번 그랬어요. 남편이 바로 옆에 있는 것처럼 완전히 진짜같이 들려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 최근에 술이나 대마초, 다른 기호용 약물을 사용하신 적이 있나요, 아니면 이게 시작될 즈음에 새로 복용하기 시작한 약이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 뭘 해당시켜야 할지 잘 모르겠어요. 시작될 즈음에 딱히 달라진 게 있었던 건 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이렇게 이름 부르는 소리를 처음 듣기 시작하신 때를 떠올려보면, 며칠 전 혹은 몇 주 전부터 시작됐나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 한 3주 정도 된 것 같아요. 긴장되고 안절부절못하는 상태에서, 이름 소리가 들리기 시작하고, 그러다 무너지기까지, 이 변화 전체가 그 정도 기간 동안 이어졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이름 부르는 소리가 유난히 들뜨거나 유난히 가라앉아 있을 때만 들리나요, 아니면 기분이 평소와 비슷할 때도 들리나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 제 생각엔 유난히 들떠 있을 때만 그랬던 것 같아요—거의 잠을 못 자고, 쉬지 않고 말하고, 모든 걸 다 고쳐야 할 것 같은 느낌이 들 때요. 그 전에는 그 목소리가 없었고, 그 후에 가라앉고 위축되는 시기로 떨어진 뒤로는 다시 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진단명: 정신병적 양상을 동반한 제1형 양극성장애 (D010)
 인구통계: 성별 여성 / 나이 48 / 직업상태 stocker or order filler / 최종학력 고등학교 졸업
@@ -575,191 +684,47 @@
 증상 지속 기간: None
 추가 요건: delusions_and_hallucinations occur exclusively during the manic episode
 주호소 증상 코드: S020
-배경 서술: 앨리슨은 은퇴 후 공예 사업을 계획하는 데 저녁 시간을 쓰고, 창고 초과근무와 가계도 조사 프로젝트에 맞춰 집안 일과를 재편하기 시작하면서 남편과 평소보다 훨씬 더 자주 다투게 되었다. 3주에 걸쳐 부부간의 긴장은 임상적으로 유의미한 변화와 맞물렸는데, 평소와 다르게 에너지가 넘치고 예민하며 말이 많은 계획 세우기와 수면 부족에서 시작해, 생생한 환각 경험으로, 그리고 이어서 뜨개질과 원예, 교회 식료품 나눔 봉사, 독서 모임에서 손을 뗀 우울한 시기로 이어졌다. 식욕과 수면이 흐트러졌고, 직장에서 재고 관리 실수를 반복했으며, 자신의 실용적이고 안정적인 평소 모습과는 너무나 달라서 스스로도 두려운, 죽음에 대한 반복적인 생각이 들기 시작했다. 그녀는 피로감 때문에 예정되어 있던 1차 진료 방문에서 이를 처음 털어놓았고, 담당 의사는 남편의 지지 속에 긴급 정신과 평가를 주선했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요—저는 스미스 선생입니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제 이름을 부르는 소리가 계속 들려서 왔어요. 집에 있을 땐 복도 쪽에서 들리는 것 같고, 창고에서도 한 번 그랬는데—아무도 없었어요. 남편이 바로 옆에 서 있는 것처럼 진짜같이 들려서, 그게 무서웠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이렇게 이름 부르는 소리를 들으신 지 얼마나 되셨나요—며칠, 몇 주, 아니면 그보다 더 오래되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 이렇게 병원까지 오게 될 만큼 무서워진 지는 꽤 됐어요. 집에서는 복도 쪽에서 제 이름이 들리고, 창고에서도 한 번 그랬어요. 남편이 바로 옆에 있는 것처럼 완전히 진짜같이 들려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 최근에 술이나 대마초, 다른 기호용 약물을 사용하신 적이 있나요, 아니면 이게 시작될 즈음에 새로 복용하기 시작한 약이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 뭘 해당시켜야 할지 잘 모르겠어요. 시작될 즈음에 딱히 달라진 게 있었던 건 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이렇게 이름 부르는 소리를 처음 듣기 시작하신 때를 떠올려보면, 며칠 전 혹은 몇 주 전부터 시작됐나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 한 3주 정도 된 것 같아요. 긴장되고 안절부절못하는 상태에서, 이름 소리가 들리기 시작하고, 그러다 무너지기까지, 이 변화 전체가 그 정도 기간 동안 이어졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이름 부르는 소리가 유난히 들뜨거나 유난히 가라앉아 있을 때만 들리나요, 아니면 기분이 평소와 비슷할 때도 들리나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 제 생각엔 유난히 들떠 있을 때만 그랬던 것 같아요—거의 잠을 못 자고, 쉬지 않고 말하고, 모든 걸 다 고쳐야 할 것 같은 느낌이 들 때요. 그 전에는 그 목소리가 없었고, 그 후에 가라앉고 위축되는 시기로 떨어진 뒤로는 다시 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+배경 서술: 앨리슨은 은퇴 후 공예 사업을 계획하는 데 저녁 시간을 쓰고, 창고 초과근무와 가계도 조사 프로젝트에 맞춰 집안 일과를 재편하기 시작하면서 남편과 평소보다 훨씬 더 자주 다투게 되었다. 3주에 걸쳐 부부간의 긴장은 임상적으로 유의미한 변화와 맞물렸는데, 평소와 다르게 에너지가 넘치고 예민하며 말이 많은 계획 세우기와 수면 부족에서 시작해, 생생한 환각 경험으로, 그리고 이어서 뜨개질과 원예, 교회 식료품 나눔 봉사, 독서 모임에서 손을 뗀 우울한 시기로 이어졌다. 식욕과 수면이 흐트러졌고, 직장에서 재고 관리 실수를 반복했으며, 자신의 실용적이고 안정적인 평소 모습과는 너무나 달라서 스스로도 두려운, 죽음에 대한 반복적인 생각이 들기 시작했다. 그녀는 피로감 때문에 예정되어 있던 1차 진료 방문에서 이를 처음 털어놓았고, 담당 의사는 남편의 지지 속에 긴급 정신과 평가를 주선했다.
+표집된 증상 목록:
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S036 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - S037 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.
+  - S038 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 정신병적 양상을 동반한 제1형 양극성장애 (D010, ICD: F31.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=2, 커버리지=0.4)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
-  누락: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
+          <t>의사의 최종 진단: 정신병적 양상을 동반한 제1형 양극성장애 (D010, ICD: F31.2)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: 있음
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=2, 커버리지=0.4)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D010_S003_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S003_P002__claude-sonnet-5_kor.xlsx
@@ -670,6 +670,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -720,11 +725,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D010_S003_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S003_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1815</v>
+        <v>0.1867</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1815</v>
+        <v>0.1867</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.7</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
